--- a/data/trans_camb/IP16_n_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,64; 23,32</t>
+          <t>-36,23; 22,56</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-66,47; -23,29</t>
+          <t>-66,96; -23,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-60,75; -13,38</t>
+          <t>-59,82; -14,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,85; -0,4</t>
+          <t>-55,48; -1,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,69; 0,39</t>
+          <t>-56,57; -0,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,65; -1,51</t>
+          <t>-56,95; -2,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,04; 1,25</t>
+          <t>-39,66; 3,59</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-52,13; -18,28</t>
+          <t>-54,46; -17,56</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-52,73; -15,72</t>
+          <t>-50,66; -15,68</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-64,33; 98,1</t>
+          <t>-65,04; 84,68</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -793,37 +793,37 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-94,98; -37,42</t>
+          <t>-96,41; -45,0</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 2,6</t>
+          <t>-96,65; 18,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,43; 13,44</t>
+          <t>-92,64; 8,13</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,44; 22,4</t>
+          <t>-95,25; 2,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-72,89; 9,47</t>
+          <t>-71,41; 17,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-94,84; -49,99</t>
+          <t>-95,4; -48,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-92,49; -48,25</t>
+          <t>-91,11; -45,75</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-50,21; -6,89</t>
+          <t>-49,99; -6,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-51,02; -9,73</t>
+          <t>-53,06; -9,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 8,43</t>
+          <t>-51,94; 7,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,69; -18,0</t>
+          <t>-56,69; -18,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-36,38; 11,67</t>
+          <t>-35,59; 14,16</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 11,79</t>
+          <t>-32,52; 9,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-46,71; -19,17</t>
+          <t>-48,48; -20,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,59; -6,84</t>
+          <t>-38,4; -6,03</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,95; 0,08</t>
+          <t>-37,39; 1,26</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,71; -6,51</t>
+          <t>-92,16; -13,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-93,83; -25,62</t>
+          <t>-92,35; -21,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-86,32; 21,89</t>
+          <t>-85,29; 22,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-95,6; -42,29</t>
+          <t>-96,12; -51,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-63,14; 41,65</t>
+          <t>-62,97; 50,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,54; 40,84</t>
+          <t>-54,46; 34,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-90,57; -53,5</t>
+          <t>-91,03; -53,77</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-75,1; -18,06</t>
+          <t>-73,67; -14,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-74,21; -0,07</t>
+          <t>-73,28; 2,16</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-54,57; 7,61</t>
+          <t>-49,61; 11,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-59,59; 3,02</t>
+          <t>-56,54; 4,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-47,33; 10,66</t>
+          <t>-44,94; 15,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 19,43</t>
+          <t>-27,0; 21,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,57; -6,03</t>
+          <t>-47,97; -5,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-25,98; 25,44</t>
+          <t>-23,98; 25,36</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-32,15; 8,65</t>
+          <t>-31,05; 7,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,81; -8,41</t>
+          <t>-45,18; -7,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-31,28; 10,64</t>
+          <t>-27,39; 11,93</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1215,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-89,81; 36,78</t>
+          <t>-82,27; 59,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 51,43</t>
+          <t>-100,0; 44,36</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 45,71</t>
+          <t>-73,27; 70,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-78,74; 263,66</t>
+          <t>-69,61; 334,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,47; 345,78</t>
+          <t>-69,42; 369,02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 51,54</t>
+          <t>-68,77; 39,3</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -9,49</t>
+          <t>-100,0; -12,08</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-63,58; 51,18</t>
+          <t>-58,64; 55,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-45,63; 0,91</t>
+          <t>-46,54; -0,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 11,2</t>
+          <t>-38,03; 10,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-28,72; 27,76</t>
+          <t>-31,47; 28,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-68,49; -15,78</t>
+          <t>-67,75; -14,85</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-73,21; -29,12</t>
+          <t>-72,2; -28,56</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 19,51</t>
+          <t>-46,39; 20,39</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-50,85; -14,29</t>
+          <t>-51,19; -14,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-50,37; -16,15</t>
+          <t>-49,55; -16,26</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 14,23</t>
+          <t>-32,69; 15,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-89,72; 34,62</t>
+          <t>-92,52; 10,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-68,51; 65,91</t>
+          <t>-74,99; 55,3</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-67,44; 138,35</t>
+          <t>-68,42; 128,95</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-93,67; -29,01</t>
+          <t>-98,38; -34,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-96,83; -60,17</t>
+          <t>-96,38; -59,03</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-81,78; 40,9</t>
+          <t>-69,98; 44,61</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,49; -34,87</t>
+          <t>-87,55; -36,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-84,5; -42,7</t>
+          <t>-83,98; -41,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-58,8; 38,16</t>
+          <t>-57,24; 40,91</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 14,28</t>
+          <t>-53,19; 13,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-58,14; 14,78</t>
+          <t>-57,89; 13,34</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 44,09</t>
+          <t>-32,33; 42,87</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-47,63; 17,04</t>
+          <t>-51,33; 15,86</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-51,16; 17,09</t>
+          <t>-50,36; 22,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 32,65</t>
+          <t>-43,57; 29,17</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-41,84; 4,92</t>
+          <t>-40,04; 4,38</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,25; 4,11</t>
+          <t>-46,75; 5,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-28,75; 25,6</t>
+          <t>-25,0; 26,34</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,96; 107,74</t>
+          <t>-87,09; 74,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 99,2</t>
+          <t>-100,0; 144,21</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,84; 255,58</t>
+          <t>-47,82; 217,5</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 187,88</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-80,49; —</t>
+          <t>-81,82; 340,69</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 29,98</t>
+          <t>-81,89; 31,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-90,43; 44,53</t>
+          <t>-100,0; 38,92</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,21; 113,88</t>
+          <t>-51,81; 120,12</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-60,63; 3,52</t>
+          <t>-56,63; 2,43</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-73,51; -27,42</t>
+          <t>-73,14; -27,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-66,32; -7,57</t>
+          <t>-67,28; -15,36</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-82,42; -36,32</t>
+          <t>-82,45; -34,97</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-70,82; -2,34</t>
+          <t>-75,92; -3,51</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 11,55</t>
+          <t>-46,61; 12,66</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-64,07; -26,45</t>
+          <t>-64,28; -25,91</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-65,6; -23,77</t>
+          <t>-66,03; -23,75</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-46,02; -1,46</t>
+          <t>-48,16; -4,69</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1863,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-92,17; 23,94</t>
+          <t>-90,54; 40,03</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1873,37 +1873,37 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -3,84</t>
+          <t>-100,0; -12,36</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -64,2</t>
+          <t>-100,0; -44,71</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 8,54</t>
+          <t>-100,0; 5,59</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-65,91; 24,97</t>
+          <t>-61,81; 30,85</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-95,37; -56,68</t>
+          <t>-95,52; -52,35</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -37,59</t>
+          <t>-100,0; -39,64</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-69,3; -3,99</t>
+          <t>-72,23; -8,89</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 8,9</t>
+          <t>-28,45; 9,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-24,51; 23,05</t>
+          <t>-23,29; 25,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4,03; 46,02</t>
+          <t>1,32; 46,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-48,05; -12,57</t>
+          <t>-47,05; -12,85</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-46,76; -4,62</t>
+          <t>-47,18; -1,46</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 19,32</t>
+          <t>-22,56; 17,89</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-35,36; -7,42</t>
+          <t>-34,77; -6,81</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,09; 3,83</t>
+          <t>-30,21; 3,5</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 25,39</t>
+          <t>-6,32; 26,23</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,07; 68,77</t>
+          <t>-78,69; 116,99</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-72,13; 173,46</t>
+          <t>-70,14; 205,45</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>9,95; 345,28</t>
+          <t>1,83; 369,51</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-94,39; -29,42</t>
+          <t>-94,18; -35,91</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -1,31</t>
+          <t>-100,0; 4,11</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 68,44</t>
+          <t>-46,85; 69,01</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-81,49; -24,64</t>
+          <t>-83,23; -20,3</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,63; 18,48</t>
+          <t>-75,98; 18,88</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-16,76; 101,96</t>
+          <t>-14,88; 114,5</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-45,46; -8,66</t>
+          <t>-44,69; -9,08</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -11,84</t>
+          <t>-46,51; -11,29</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 46,78</t>
+          <t>-14,72; 47,89</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 19,33</t>
+          <t>-20,78; 18,34</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-32,83; -4,94</t>
+          <t>-32,31; -3,53</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,92; 59,94</t>
+          <t>4,9; 57,81</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-27,28; -1,93</t>
+          <t>-27,14; 0,5</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-35,14; -13,2</t>
+          <t>-34,18; -12,44</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,63; 44,23</t>
+          <t>4,16; 45,02</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-94,32; -21,0</t>
+          <t>-93,25; -19,48</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -38,05</t>
+          <t>-94,52; -34,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-37,23; 169,77</t>
+          <t>-35,24; 166,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-63,9; 95,43</t>
+          <t>-63,08; 98,22</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-93,3; -10,01</t>
+          <t>-92,37; -5,0</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>21,67; 314,49</t>
+          <t>13,29; 285,33</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -2,52</t>
+          <t>-74,18; 4,17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-91,9; -47,25</t>
+          <t>-90,65; -40,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>6,6; 169,47</t>
+          <t>11,75; 174,55</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -10,7</t>
+          <t>-29,14; -12,02</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-34,38; -17,62</t>
+          <t>-33,92; -17,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-24,25; 0,87</t>
+          <t>-22,94; 0,87</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-34,67; -18,4</t>
+          <t>-34,22; -18,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-34,3; -17,67</t>
+          <t>-33,04; -17,31</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 3,21</t>
+          <t>-14,84; 3,11</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-29,05; -17,3</t>
+          <t>-29,36; -16,78</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-31,7; -20,09</t>
+          <t>-31,74; -20,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-16,51; -1,25</t>
+          <t>-18,09; -1,19</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-66,58; -32,2</t>
+          <t>-67,33; -34,64</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-78,25; -50,6</t>
+          <t>-79,05; -52,49</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-57,26; 2,23</t>
+          <t>-55,0; 2,17</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-77,79; -51,18</t>
+          <t>-76,48; -50,67</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-76,94; -47,28</t>
+          <t>-76,58; -48,5</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-34,54; 8,91</t>
+          <t>-33,44; 9,03</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-69,38; -47,67</t>
+          <t>-69,16; -48,71</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-75,28; -55,25</t>
+          <t>-75,02; -56,05</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-39,98; -4,15</t>
+          <t>-41,98; -3,37</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16_n_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16_n_R2-Provincia-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumen más de dos medicamentos</t>
+          <t>Menores que consumieron más de dos medicamentos en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-28,44</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-27,44</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-30,78</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-8,37</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-44,36</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-36,05</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-28,44</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-27,44</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-30,76</t>
+          <t>-33,03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-33,57</t>
+          <t>-31,87</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-36,23; 22,56</t>
+          <t>-55,72; -1,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-66,96; -23,65</t>
+          <t>-54,69; -1,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-59,82; -14,76</t>
+          <t>-54,88; -2,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-55,48; -1,57</t>
+          <t>-35,78; 24,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -0,93</t>
+          <t>-66,21; -22,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-56,95; -2,83</t>
+          <t>-55,65; -8,32</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-39,66; 3,59</t>
+          <t>-39,62; 1,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-54,46; -17,56</t>
+          <t>-54,42; -18,48</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-50,66; -15,68</t>
+          <t>-48,93; -13,15</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-68,34%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-65,95%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-73,97%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-18,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-81,27%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-68,34%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-65,95%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-73,93%</t>
+          <t>-74,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-78,15%</t>
+          <t>-74,19%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-65,04; 84,68</t>
+          <t>-93,42; 29,04</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>-91,32; 10,12</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>-95,65; 24,44</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>-62,59; 93,22</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-96,41; -45,0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-96,65; 18,58</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-92,64; 8,13</t>
-        </is>
-      </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-95,25; 2,31</t>
+          <t>-92,4; -23,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-71,41; 17,84</t>
+          <t>-72,84; 6,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-95,4; -48,25</t>
+          <t>-94,99; -52,83</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-91,11; -45,75</t>
+          <t>-88,79; -35,79</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-36,92</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-11,89</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-10,89</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-28,75</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-30,56</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-17,78</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-36,92</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-11,89</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-10,32</t>
+          <t>-4,74</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-14,91</t>
+          <t>-8,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-49,99; -6,04</t>
+          <t>-59,0; -19,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-53,06; -9,8</t>
+          <t>-34,52; 14,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-51,94; 7,17</t>
+          <t>-30,77; 9,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-56,69; -18,46</t>
+          <t>-49,21; -7,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,59; 14,16</t>
+          <t>-52,49; -10,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,52; 9,39</t>
+          <t>-28,47; 19,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-48,48; -20,1</t>
+          <t>-47,34; -18,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-38,4; -6,03</t>
+          <t>-38,53; -5,64</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-37,39; 1,26</t>
+          <t>-23,58; 8,59</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-83,51%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-26,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-24,64%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-70,3%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-74,73%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-43,48%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-83,51%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-26,89%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-23,34%</t>
+          <t>-11,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-34,93%</t>
+          <t>-18,8%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-92,16; -13,73</t>
+          <t>-95,9; -47,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-92,35; -21,15</t>
+          <t>-63,7; 50,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-85,29; 22,44</t>
+          <t>-55,07; 33,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-96,12; -51,55</t>
+          <t>-91,14; -20,25</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-62,97; 50,78</t>
+          <t>-93,7; -26,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,46; 34,39</t>
+          <t>-50,61; 75,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-91,03; -53,77</t>
+          <t>-89,94; -48,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-73,67; -14,12</t>
+          <t>-73,49; -17,44</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-73,28; 2,16</t>
+          <t>-44,73; 27,44</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-2,05</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-23,73</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,18</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-21,12</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-29,41</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-16,02</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-2,05</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-23,73</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,1</t>
+          <t>-16,93</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,04</t>
+          <t>-9,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 11,04</t>
+          <t>-28,78; 19,83</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-56,54; 4,69</t>
+          <t>-52,56; -5,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-44,94; 15,48</t>
+          <t>-27,26; 23,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,0; 21,99</t>
+          <t>-50,43; 8,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-47,97; -5,99</t>
+          <t>-56,7; 5,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 25,36</t>
+          <t>-43,89; 10,61</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,05; 7,84</t>
+          <t>-32,3; 7,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-45,18; -7,18</t>
+          <t>-43,98; -7,89</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 11,93</t>
+          <t>-30,25; 9,74</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-8,65%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-4,99%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-48,06%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-66,91%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-36,44%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-8,65%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>-38,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-23,42%</t>
+          <t>-27,9%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-82,27; 59,9</t>
+          <t>-70,94; 287,8</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 44,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-73,27; 70,97</t>
+          <t>-71,56; 389,71</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-69,61; 334,58</t>
+          <t>-84,7; 43,2</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 56,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,42; 369,02</t>
+          <t>-71,98; 46,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-68,77; 39,3</t>
+          <t>-68,22; 43,53</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -12,08</t>
+          <t>-100,0; -11,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 55,38</t>
+          <t>-63,2; 44,61</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-44,91</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-53,58</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-16,07</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-21,18</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-11,59</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-44,91</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-53,58</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-15,99</t>
+          <t>-0,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-9,36</t>
+          <t>-8,74</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -0,04</t>
+          <t>-68,04; -18,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-38,03; 10,24</t>
+          <t>-71,94; -28,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-31,47; 28,35</t>
+          <t>-51,51; 22,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-67,75; -14,85</t>
+          <t>-42,31; 3,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-72,2; -28,56</t>
+          <t>-36,59; 11,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 20,39</t>
+          <t>-30,69; 32,83</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-51,19; -14,91</t>
+          <t>-51,96; -16,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-49,55; -16,26</t>
+          <t>-48,86; -16,81</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-32,69; 15,7</t>
+          <t>-34,0; 13,33</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-73,24%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-87,39%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-26,2%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-60,85%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-33,32%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-5,46%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-73,24%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-87,39%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-26,08%</t>
+          <t>-1,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-19,46%</t>
+          <t>-18,18%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-92,52; 10,45</t>
+          <t>-93,2; -25,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-74,99; 55,3</t>
+          <t>-96,52; -58,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,42; 128,95</t>
+          <t>-73,53; 50,87</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-98,38; -34,06</t>
+          <t>-89,97; 47,39</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-96,38; -59,03</t>
+          <t>-71,44; 63,33</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-69,98; 44,61</t>
+          <t>-66,68; 172,33</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-87,55; -36,8</t>
+          <t>-87,69; -42,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-83,98; -41,16</t>
+          <t>-85,3; -43,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,24; 40,91</t>
+          <t>-59,36; 36,31</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-14,04</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-18,62</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0,44</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-19,73</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-23,89</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>8,63</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-14,04</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-18,62</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,25</t>
+          <t>11,18</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>4,55</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-53,19; 13,59</t>
+          <t>-50,72; 16,42</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-57,89; 13,34</t>
+          <t>-51,06; 16,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 42,87</t>
+          <t>-38,31; 36,57</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-51,33; 15,86</t>
+          <t>-52,01; 14,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-50,36; 22,77</t>
+          <t>-59,12; 17,62</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-43,57; 29,17</t>
+          <t>-27,34; 48,41</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-40,04; 4,38</t>
+          <t>-40,92; 4,31</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-46,75; 5,78</t>
+          <t>-45,92; 6,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-25,0; 26,34</t>
+          <t>-25,0; 28,7</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-46,14%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-61,19%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-46,72%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-56,58%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>20,43%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-46,14%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-61,19%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-10,69%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>12,36%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-87,09; 74,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 144,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 217,5</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 187,88</t>
+          <t>-89,17; 94,09</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 154,22</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-81,82; 340,69</t>
+          <t>-46,38; 266,9</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-81,89; 31,64</t>
+          <t>-79,96; 30,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 38,92</t>
+          <t>-89,99; 51,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,81; 120,12</t>
+          <t>-48,73; 124,71</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-60,29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-44,12</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-20,82</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>-31,3</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-50,07</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-42,67</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-60,29</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>-44,12</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-19,52</t>
+          <t>-42,61</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-25,35</t>
+          <t>-27,62</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-56,63; 2,43</t>
+          <t>-82,38; -33,44</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-73,14; -27,0</t>
+          <t>-71,48; -5,25</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-67,28; -15,36</t>
+          <t>-50,43; 12,02</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-82,45; -34,97</t>
+          <t>-60,46; 2,08</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-75,92; -3,51</t>
+          <t>-73,06; -27,12</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-46,61; 12,66</t>
+          <t>-67,57; -15,27</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-64,28; -25,91</t>
+          <t>-63,62; -26,13</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-66,03; -23,75</t>
+          <t>-66,74; -25,36</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-48,16; -4,69</t>
+          <t>-48,3; -5,34</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-93,52%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-68,44%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-32,29%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>-62,52%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-85,23%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-93,52%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>-68,44%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-30,28%</t>
+          <t>-85,1%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-44,67%</t>
+          <t>-48,67%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-90,54; 40,03</t>
+          <t>-100,0; -66,93</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 2,81</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>-65,07; 20,76</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>-93,85; 12,78</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -12,36</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -44,71</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 5,59</t>
-        </is>
-      </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-61,81; 30,85</t>
+          <t>-100,0; -24,06</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-95,52; -52,35</t>
+          <t>-95,43; -55,66</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -39,64</t>
+          <t>-100,0; -43,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-72,23; -8,89</t>
+          <t>-75,36; -11,01</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-31,37</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-27,76</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-1,84</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>-9,62</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>-2,08</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>25,96</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-31,37</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-27,76</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-2,9</t>
+          <t>24,97</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9,31</t>
+          <t>9,78</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 9,9</t>
+          <t>-47,88; -14,09</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-23,29; 25,06</t>
+          <t>-47,25; -0,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 46,42</t>
+          <t>-24,0; 19,28</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-47,05; -12,85</t>
+          <t>-28,66; 9,28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-47,18; -1,46</t>
+          <t>-24,28; 22,39</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 17,89</t>
+          <t>0,54; 44,56</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-34,77; -6,81</t>
+          <t>-34,38; -7,62</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-30,21; 3,5</t>
+          <t>-31,25; 2,8</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 26,23</t>
+          <t>-7,36; 24,49</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-79,47%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-70,31%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-4,67%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>-37,04%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>-8,0%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>99,95%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-79,47%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-70,31%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-7,36%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-78,69; 116,99</t>
+          <t>-100,0; -37,49</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-70,14; 205,45</t>
+          <t>-100,0; 12,17</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1,83; 369,51</t>
+          <t>-50,05; 65,45</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-94,18; -35,91</t>
+          <t>-78,19; 72,97</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 4,11</t>
+          <t>-73,58; 151,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-46,85; 69,01</t>
+          <t>1,18; 344,74</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-83,23; -20,3</t>
+          <t>-83,75; -26,65</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-75,98; 18,88</t>
+          <t>-77,16; 16,2</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-14,88; 114,5</t>
+          <t>-17,53; 103,75</t>
         </is>
       </c>
     </row>
@@ -2136,32 +2136,32 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>-2,88</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>-19,85</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>33,14</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>-27,24</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t>-28,62</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>15,28</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>-2,88</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>-19,85</t>
-        </is>
-      </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>33,37</t>
+          <t>14,7</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26,1</t>
+          <t>25,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-44,69; -9,08</t>
+          <t>-19,7; 19,27</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-46,51; -11,29</t>
+          <t>-33,25; -5,97</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 47,89</t>
+          <t>2,49; 56,64</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-20,78; 18,34</t>
+          <t>-43,22; -9,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-32,31; -3,53</t>
+          <t>-46,27; -12,34</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>4,9; 57,81</t>
+          <t>-16,35; 45,87</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-27,14; 0,5</t>
+          <t>-27,12; -0,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-34,18; -12,44</t>
+          <t>-34,39; -12,76</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>4,16; 45,02</t>
+          <t>4,66; 47,02</t>
         </is>
       </c>
     </row>
@@ -2242,32 +2242,32 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>-10,37%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>-71,36%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>119,11%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>-74,46%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>-78,24%</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>-10,37%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>-71,36%</t>
-        </is>
-      </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>119,93%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>83,45%</t>
+          <t>82,72%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-93,25; -19,48</t>
+          <t>-62,18; 94,14</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-94,52; -34,31</t>
+          <t>-92,85; -7,78</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-35,24; 166,22</t>
+          <t>9,54; 286,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-63,08; 98,22</t>
+          <t>-93,71; -22,27</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-92,37; -5,0</t>
+          <t>-95,02; -33,53</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,29; 285,33</t>
+          <t>-36,92; 161,98</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-74,18; 4,17</t>
+          <t>-73,98; -1,67</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-90,65; -40,64</t>
+          <t>-90,23; -44,52</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>11,75; 174,55</t>
+          <t>12,83; 187,05</t>
         </is>
       </c>
     </row>
@@ -2352,32 +2352,32 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-26,01</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-26,0</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>-5,87</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>-20,33</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t>-25,71</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-9,75</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>-26,01</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>-26,0</t>
-        </is>
-      </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-6,2</t>
+          <t>-3,55</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-4,79</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -12,02</t>
+          <t>-33,59; -17,53</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-33,92; -17,92</t>
+          <t>-33,68; -16,99</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-22,94; 0,87</t>
+          <t>-14,16; 4,27</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-34,22; -18,22</t>
+          <t>-28,62; -11,14</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-33,04; -17,31</t>
+          <t>-34,7; -18,28</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-14,84; 3,11</t>
+          <t>-12,46; 5,4</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-29,36; -16,78</t>
+          <t>-29,1; -17,2</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-31,74; -20,17</t>
+          <t>-31,9; -19,75</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-18,09; -1,19</t>
+          <t>-11,18; 2,52</t>
         </is>
       </c>
     </row>
@@ -2458,32 +2458,32 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-65,38%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-65,35%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>-14,74%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>-53,15%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t>-67,21%</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-25,48%</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>-65,38%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
-        <is>
-          <t>-65,35%</t>
-        </is>
-      </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-15,57%</t>
+          <t>-9,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-20,46%</t>
+          <t>-12,26%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-67,33; -34,64</t>
+          <t>-76,87; -49,48</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-79,05; -52,49</t>
+          <t>-76,87; -47,96</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-55,0; 2,17</t>
+          <t>-31,86; 12,88</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-76,48; -50,67</t>
+          <t>-66,91; -33,23</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-76,58; -48,5</t>
+          <t>-80,14; -51,99</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-33,44; 9,03</t>
+          <t>-28,72; 16,59</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-69,16; -48,71</t>
+          <t>-69,57; -48,11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-75,02; -56,05</t>
+          <t>-75,38; -54,76</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-41,98; -3,37</t>
+          <t>-26,59; 7,69</t>
         </is>
       </c>
     </row>
